--- a/tame_output/ON/bt/strategyON_20240821.xlsx
+++ b/tame_output/ON/bt/strategyON_20240821.xlsx
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-160.3%</t>
+          <t>-160.4%</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>14.5%</t>
         </is>
       </c>
     </row>
@@ -47821,7 +47821,7 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378393</v>
+        <v>3.749882691378394</v>
       </c>
       <c r="C2012" t="n">
         <v>3.466880608322168</v>
@@ -47844,7 +47844,7 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006976</v>
+        <v>3.715819895006977</v>
       </c>
       <c r="C2013" t="n">
         <v>3.46540464944917</v>
@@ -47867,7 +47867,7 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787387</v>
+        <v>3.684895778787388</v>
       </c>
       <c r="C2014" t="n">
         <v>3.462169093426369</v>
@@ -47890,7 +47890,7 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585938</v>
+        <v>3.619348081585939</v>
       </c>
       <c r="C2015" t="n">
         <v>3.528875053016873</v>
@@ -47913,7 +47913,7 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814665</v>
+        <v>3.640750087814666</v>
       </c>
       <c r="C2016" t="n">
         <v>3.66918677201872</v>
@@ -47936,7 +47936,7 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237094</v>
+        <v>3.668289004237095</v>
       </c>
       <c r="C2017" t="n">
         <v>3.73816704116436</v>
@@ -47959,7 +47959,7 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423387</v>
+        <v>3.619923016423388</v>
       </c>
       <c r="C2018" t="n">
         <v>3.724218243284481</v>
@@ -47982,7 +47982,7 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609753</v>
+        <v>3.656332733609754</v>
       </c>
       <c r="C2019" t="n">
         <v>3.736088732339895</v>
@@ -48005,7 +48005,7 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973158</v>
+        <v>3.674028535973159</v>
       </c>
       <c r="C2020" t="n">
         <v>3.737299266858838</v>
@@ -48028,7 +48028,7 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251946</v>
+        <v>3.663509457251947</v>
       </c>
       <c r="C2021" t="n">
         <v>3.74142100908616</v>
@@ -48051,7 +48051,7 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916202</v>
+        <v>3.652149152916203</v>
       </c>
       <c r="C2022" t="n">
         <v>3.736498861822349</v>
@@ -48074,7 +48074,7 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830329</v>
+        <v>3.66796230683033</v>
       </c>
       <c r="C2023" t="n">
         <v>3.898702918521393</v>
@@ -48097,7 +48097,7 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071551</v>
+        <v>3.696539468071552</v>
       </c>
       <c r="C2024" t="n">
         <v>3.893549556485207</v>
@@ -48120,7 +48120,7 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868145</v>
+        <v>3.750044015868147</v>
       </c>
       <c r="C2025" t="n">
         <v>3.903778974053699</v>
@@ -48143,7 +48143,7 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.78363286733269</v>
+        <v>3.783632867332692</v>
       </c>
       <c r="C2026" t="n">
         <v>3.912704612509601</v>
@@ -48166,7 +48166,7 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231807</v>
+        <v>3.798296784231809</v>
       </c>
       <c r="C2027" t="n">
         <v>3.904857499753776</v>
@@ -48189,7 +48189,7 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818522</v>
+        <v>3.785563924818524</v>
       </c>
       <c r="C2028" t="n">
         <v>3.909107510475751</v>
@@ -48212,7 +48212,7 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051788</v>
+        <v>3.77723741205179</v>
       </c>
       <c r="C2029" t="n">
         <v>3.916368393358287</v>
@@ -48235,7 +48235,7 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679624</v>
+        <v>3.812635940679626</v>
       </c>
       <c r="C2030" t="n">
         <v>3.917339571110997</v>
@@ -48258,7 +48258,7 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474159</v>
+        <v>3.821184182474161</v>
       </c>
       <c r="C2031" t="n">
         <v>3.918182475490752</v>
@@ -48281,7 +48281,7 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969543</v>
+        <v>3.831734516969544</v>
       </c>
       <c r="C2032" t="n">
         <v>3.937220574364898</v>
@@ -48304,7 +48304,7 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700478</v>
+        <v>3.82575293270048</v>
       </c>
       <c r="C2033" t="n">
         <v>3.753404570488832</v>
@@ -48327,7 +48327,7 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077639</v>
+        <v>3.804688961077641</v>
       </c>
       <c r="C2034" t="n">
         <v>3.756906614562796</v>
@@ -48350,7 +48350,7 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833457</v>
+        <v>3.775028860833459</v>
       </c>
       <c r="C2035" t="n">
         <v>3.741333433638879</v>
@@ -48373,7 +48373,7 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077628</v>
+        <v>3.821030660077629</v>
       </c>
       <c r="C2036" t="n">
         <v>3.740521144075308</v>
@@ -48396,7 +48396,7 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147909</v>
+        <v>3.83230702414791</v>
       </c>
       <c r="C2037" t="n">
         <v>3.750389923200381</v>
@@ -48419,7 +48419,7 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.83441549373528</v>
+        <v>3.834415493735282</v>
       </c>
       <c r="C2038" t="n">
         <v>3.821226928976806</v>
@@ -48442,7 +48442,7 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496553</v>
+        <v>3.855120535496555</v>
       </c>
       <c r="C2039" t="n">
         <v>3.818095939795104</v>
@@ -48465,7 +48465,7 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108855</v>
+        <v>3.815643212108857</v>
       </c>
       <c r="C2040" t="n">
         <v>3.822626834734496</v>
@@ -48488,7 +48488,7 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121465</v>
+        <v>3.807356168121466</v>
       </c>
       <c r="C2041" t="n">
         <v>3.822756088213039</v>
@@ -48511,7 +48511,7 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906078</v>
+        <v>3.77523303390608</v>
       </c>
       <c r="C2042" t="n">
         <v>3.802592933950636</v>
@@ -48534,7 +48534,7 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912983</v>
+        <v>3.785761685912985</v>
       </c>
       <c r="C2043" t="n">
         <v>3.837559870562694</v>
@@ -48557,7 +48557,7 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539893</v>
+        <v>3.743767956539894</v>
       </c>
       <c r="C2044" t="n">
         <v>3.831246438464132</v>
@@ -48580,7 +48580,7 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811007</v>
+        <v>3.725010844811009</v>
       </c>
       <c r="C2045" t="n">
         <v>3.833127068648268</v>
@@ -48603,7 +48603,7 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382918</v>
+        <v>3.61232244438292</v>
       </c>
       <c r="C2046" t="n">
         <v>3.84597809452615</v>
@@ -48626,7 +48626,7 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760314</v>
+        <v>3.646857607760317</v>
       </c>
       <c r="C2047" t="n">
         <v>3.866180764699744</v>
@@ -48649,7 +48649,7 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781705</v>
+        <v>3.666767386781708</v>
       </c>
       <c r="C2048" t="n">
         <v>3.866180764699744</v>
@@ -48672,7 +48672,7 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082834</v>
+        <v>3.670068888082837</v>
       </c>
       <c r="C2049" t="n">
         <v>3.826432678293211</v>
@@ -48695,7 +48695,7 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943585</v>
+        <v>3.745593333943589</v>
       </c>
       <c r="C2050" t="n">
         <v>3.833455297290151</v>
@@ -48718,7 +48718,7 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677824</v>
+        <v>3.730590658677827</v>
       </c>
       <c r="C2051" t="n">
         <v>3.932626296863055</v>
@@ -48741,7 +48741,7 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073883</v>
+        <v>3.741298518073886</v>
       </c>
       <c r="C2052" t="n">
         <v>4.120092521771348</v>
@@ -48764,7 +48764,7 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699135800903168</v>
+        <v>3.699135800903171</v>
       </c>
       <c r="C2053" t="n">
         <v>4.08949547312543</v>
@@ -48787,7 +48787,7 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568382</v>
+        <v>3.708202704568386</v>
       </c>
       <c r="C2054" t="n">
         <v>4.093171875787148</v>
@@ -48810,7 +48810,7 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740601586682204</v>
+        <v>3.740601586682208</v>
       </c>
       <c r="C2055" t="n">
         <v>4.090789930910643</v>
@@ -48833,7 +48833,7 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539107</v>
+        <v>3.699424827539111</v>
       </c>
       <c r="C2056" t="n">
         <v>4.088083170068278</v>
@@ -48856,7 +48856,7 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983737</v>
+        <v>3.689962785983741</v>
       </c>
       <c r="C2057" t="n">
         <v>4.089511972211512</v>
@@ -48879,7 +48879,7 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711872614969749</v>
+        <v>3.711872614969752</v>
       </c>
       <c r="C2058" t="n">
         <v>4.189443211469265</v>
@@ -48902,7 +48902,7 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714899237073539</v>
+        <v>3.714899237073542</v>
       </c>
       <c r="C2059" t="n">
         <v>4.187228908595204</v>
@@ -48925,7 +48925,7 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704778134720065</v>
+        <v>3.704778134720069</v>
       </c>
       <c r="C2060" t="n">
         <v>4.187132036669493</v>
@@ -48948,7 +48948,7 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736825137581133</v>
+        <v>3.736825137581136</v>
       </c>
       <c r="C2061" t="n">
         <v>4.187125930227537</v>
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.809818689622985</v>
+        <v>3.809818689622989</v>
       </c>
       <c r="C2062" t="n">
         <v>4.185222326790147</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.065232122433597</v>
+        <v>-5.065553351838039</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.158773053502961</v>
+        <v>2.158644561741184</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.7010373081683903</v>
+        <v>0.7007160787639487</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.605844711691182</v>
+        <v>4.605651974048516</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240821.xlsx
+++ b/tame_output/ON/bt/strategyON_20240821.xlsx
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.7%</t>
+          <t>-78.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-41.9%</t>
+          <t>-39.8%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.5%</t>
+          <t>-48.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.8%</t>
+          <t>-74.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-3.0%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-668.1%</t>
+          <t>-664.9%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-160.4%</t>
+          <t>-159.1%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-11.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-9.8%</t>
+          <t>-8.2%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-23.7%</t>
+          <t>-23.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-329.3%</t>
+          <t>-329.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-153.9%</t>
+          <t>-150.7%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>93.6%</t>
+          <t>94.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.5%</t>
+          <t>60.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>84.8%</t>
+          <t>85.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>16.5%</t>
         </is>
       </c>
     </row>
@@ -48977,16 +48977,16 @@
         <v>4.185222326790147</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.065553351838039</v>
+        <v>-5.033053074847404</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.158644561741184</v>
+        <v>2.171644672537438</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.7007160787639487</v>
+        <v>0.7332163557545831</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.605651974048516</v>
+        <v>4.625152140242897</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240821.xlsx
+++ b/tame_output/ON/bt/strategyON_20240821.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>57.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-11.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>49.2%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>77.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.5%</t>
+          <t>-78.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.4%</t>
+          <t>107.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.2%</t>
+          <t>89.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-39.8%</t>
+          <t>-42.4%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.4%</t>
+          <t>-48.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.7%</t>
+          <t>-75.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.0%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-664.9%</t>
+          <t>-675.4%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.8%</t>
+          <t>-34.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-159.1%</t>
+          <t>-163.3%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-8.2%</t>
+          <t>-7.9%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-23.5%</t>
+          <t>-23.6%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-4.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-329.0%</t>
+          <t>-328.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-150.7%</t>
+          <t>-151.7%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>94.3%</t>
+          <t>94.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.4%</t>
+          <t>60.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>85.3%</t>
+          <t>85.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>15.9%</t>
         </is>
       </c>
     </row>
@@ -48195,16 +48195,16 @@
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.240885473559752</v>
+        <v>-5.307151357315617</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.812396896738103</v>
+        <v>1.785890543235757</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.1644018277749375</v>
+        <v>0.1934050180593213</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.007748607140713</v>
+        <v>4.025150521311343</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.939438748087914</v>
+        <v>-5.00570463184378</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.940236469809374</v>
+        <v>1.913730116307027</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.4658485532467748</v>
+        <v>0.4948517435311586</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.195877525306352</v>
+        <v>4.213279439476982</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.964028992323098</v>
+        <v>-5.030294876078964</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.931371549868011</v>
+        <v>1.904865196365665</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.4658485532467748</v>
+        <v>0.4948517435311586</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.196848703059063</v>
+        <v>4.214250617229693</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.912990616316578</v>
+        <v>-4.979256500072443</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.952629804650374</v>
+        <v>1.926123451148028</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.4658485532467748</v>
+        <v>0.4948517435311586</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.197691607438817</v>
+        <v>4.215093521609448</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.871851321449947</v>
+        <v>-4.938117205205812</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.988123621471172</v>
+        <v>1.961617267968825</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.5069878481134056</v>
+        <v>0.5359910383977894</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.241413283232942</v>
+        <v>4.258815197403572</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.775216409431307</v>
+        <v>-4.841482293187172</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.842961582402562</v>
+        <v>1.816455228900216</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.6036227601320455</v>
+        <v>0.6326259504164293</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.11557822656806</v>
+        <v>4.13298014073869</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.905797143962149</v>
+        <v>-4.972063027718015</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.794231332664189</v>
+        <v>1.767724979161843</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.473042025601203</v>
+        <v>0.5020452158855868</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.040731829923518</v>
+        <v>4.058133744094149</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.741300809771188</v>
+        <v>-4.807566693527053</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.844456685416656</v>
+        <v>1.81795033191431</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.6375383597921649</v>
+        <v>0.6665415500765487</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.123856449514178</v>
+        <v>4.141258363684808</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.76867074245562</v>
+        <v>-4.834936626211485</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.832696422779313</v>
+        <v>1.806190069276967</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.6375383597921649</v>
+        <v>0.6665415500765487</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.123044159950608</v>
+        <v>4.140446074121238</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.779055937345509</v>
+        <v>-4.845321821101375</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.83841112394843</v>
+        <v>1.811904770446084</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.6271531649022756</v>
+        <v>0.6561563551866594</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.126681822141746</v>
+        <v>4.144083736312377</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.797644096067734</v>
+        <v>-4.8639099798236</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.901812866235965</v>
+        <v>1.875306512733619</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.6085650061800503</v>
+        <v>0.637568196464434</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.186365932684836</v>
+        <v>4.203767846855467</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.79794264276377</v>
+        <v>-4.864208526519636</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.898562458375849</v>
+        <v>1.872056104873503</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.6082664594840144</v>
+        <v>0.6372696497683981</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.183055815485513</v>
+        <v>4.200457729656144</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.697119509073342</v>
+        <v>-4.763385392829208</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.943422606791412</v>
+        <v>1.916916253289065</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.6207306749683682</v>
+        <v>0.6497338652527519</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.195065239715517</v>
+        <v>4.212467153886148</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.506338148320935</v>
+        <v>-4.5726040320768</v>
       </c>
       <c r="E2041" t="n">
-        <v>2.019864404570918</v>
+        <v>1.993358051068572</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.8115120357207756</v>
+        <v>0.8405152260051593</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.309663309645504</v>
+        <v>4.327065223816135</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.487821294279115</v>
+        <v>-4.55408717803498</v>
       </c>
       <c r="E2042" t="n">
-        <v>2.007107991925242</v>
+        <v>1.980601638422897</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.8244421651459838</v>
+        <v>0.8534453554303675</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.297258233038226</v>
+        <v>4.314660147208857</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.462628109777797</v>
+        <v>-4.528893993533662</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.052152202337828</v>
+        <v>2.025645848835482</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.8496353496473021</v>
+        <v>0.8786385399316858</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.347341080351075</v>
+        <v>4.364742994521706</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.450573982864834</v>
+        <v>-4.516839866620699</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.050660421004451</v>
+        <v>2.024154067502105</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.861689476560265</v>
+        <v>0.8906926668446487</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.348260124400291</v>
+        <v>4.365662038570921</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.457197229555192</v>
+        <v>-4.523463113311057</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.049891752512443</v>
+        <v>2.023385399010098</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.8550662298699065</v>
+        <v>0.8840694201542902</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.346166806570212</v>
+        <v>4.363568720740842</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.3543166400266</v>
+        <v>-4.420582523782464</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.103895014201763</v>
+        <v>2.077388660699417</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.9579468193984995</v>
+        <v>0.9869500096828832</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.42074618616525</v>
+        <v>4.43814810033588</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.377758679206686</v>
+        <v>-4.444024562962551</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.114720868703323</v>
+        <v>2.088214515200977</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.9579468193984995</v>
+        <v>0.9869500096828832</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.440948856338844</v>
+        <v>4.458350770509474</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.395831187498298</v>
+        <v>-4.462097071254163</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.107491865386678</v>
+        <v>2.080985511884332</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.9579468193984995</v>
+        <v>0.9869500096828832</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.440948856338844</v>
+        <v>4.458350770509474</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.62700498137493</v>
+        <v>-4.693270865130795</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.975274261429492</v>
+        <v>1.948767907927146</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.9579468193984995</v>
+        <v>0.9869500096828832</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.401200769932311</v>
+        <v>4.418602684102941</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.595718960834475</v>
+        <v>-4.661984844590339</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.994811288642614</v>
+        <v>1.968304935140268</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.9892328399389547</v>
+        <v>1.018236030223338</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.426995001253524</v>
+        <v>4.444396915424154</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.44269356872119</v>
+        <v>-4.508959452477055</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.155192445060831</v>
+        <v>2.128686091558486</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.142258232052239</v>
+        <v>1.171261422336622</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.617981236094399</v>
+        <v>4.635383150265029</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>4.120092521771348</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.471000882594461</v>
+        <v>-4.537266766350325</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.331335744419816</v>
+        <v>2.30482939091747</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.142258232052239</v>
+        <v>1.171261422336622</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.805447461002691</v>
+        <v>4.822849375173321</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>4.08949547312543</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.637594107707983</v>
+        <v>-4.703859991463847</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.234101405728489</v>
+        <v>2.207595052226144</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.9756650069387163</v>
+        <v>1.0046681972231</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.67489447728866</v>
+        <v>4.69229639145929</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>4.093171875787148</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.464529728325683</v>
+        <v>-4.530795612081548</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.307003560143127</v>
+        <v>2.280497206640781</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.9756650069387163</v>
+        <v>1.0046681972231</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.678570879950378</v>
+        <v>4.695972794121007</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>4.090789930910643</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.435283747869986</v>
+        <v>-4.501549631625851</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.316320007448901</v>
+        <v>2.289813653946555</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.9756650069387163</v>
+        <v>1.0046681972231</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.676188935073872</v>
+        <v>4.693590849244503</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>4.088083170068278</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.542209295747837</v>
+        <v>-4.608475179503702</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.270843027455395</v>
+        <v>2.244336673953049</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.8687394590608649</v>
+        <v>0.8977426493452486</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.609326845504797</v>
+        <v>4.626728759675427</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>4.089511972211512</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.687227854255086</v>
+        <v>-4.753493738010951</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.21426440619573</v>
+        <v>2.187758052693384</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.7237209005536164</v>
+        <v>0.7527240908380001</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.523744512543682</v>
+        <v>4.541146426714312</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>4.189443211469265</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.805569620039804</v>
+        <v>-4.871835503795668</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.266858939139596</v>
+        <v>2.24035258563725</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.7344069391165065</v>
+        <v>0.7634101294008901</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.630087374939169</v>
+        <v>4.647489289109799</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>4.187228908595204</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.856980042360512</v>
+        <v>-4.923245926116376</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.244080467337252</v>
+        <v>2.217574113834906</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.7344069391165065</v>
+        <v>0.7634101294008901</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.627873072065108</v>
+        <v>4.645274986235738</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>4.187132036669493</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.936399493568263</v>
+        <v>-5.002665377324128</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.212215814928441</v>
+        <v>2.185709461426095</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.7344069391165065</v>
+        <v>0.7634101294008901</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.627776200139397</v>
+        <v>4.645178114310028</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>4.187125930227537</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.031862491485481</v>
+        <v>-5.098128375241346</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.174024509319597</v>
+        <v>2.147518155817251</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.7344069391165065</v>
+        <v>0.7634101294008901</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.627770093697441</v>
+        <v>4.645172007868071</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.809818689622989</v>
+        <v>3.772338974041173</v>
       </c>
       <c r="C2062" t="n">
         <v>4.185222326790147</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.033053074847404</v>
+        <v>-5.138148373285129</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.171644672537438</v>
+        <v>2.129606553162348</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.7332163557545831</v>
+        <v>0.7233901313571063</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.625152140242897</v>
+        <v>4.619256405604411</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240821.xlsx
+++ b/tame_output/ON/bt/strategyON_20240821.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>58.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2059</v>
+        <v>2060</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.4%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>49.2%</t>
+          <t>53.1%</t>
         </is>
       </c>
     </row>
@@ -758,26 +758,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>94.2%</t>
+          <t>97.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2059</v>
+        <v>2060</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>77.9%</t>
+          <t>80.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>106.9%</t>
+          <t>118.4%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.9%</t>
+          <t>-78.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.3%</t>
+          <t>107.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2059</v>
+        <v>2060</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.5%</t>
+          <t>123.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.9%</t>
+          <t>90.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-42.4%</t>
+          <t>-39.8%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.8%</t>
+          <t>-48.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.2%</t>
+          <t>-74.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>89.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-675.4%</t>
+          <t>-664.9%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2059</v>
+        <v>2060</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.0%</t>
+          <t>-33.8%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-163.3%</t>
+          <t>-159.1%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-11.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2059</v>
+        <v>2060</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-7.9%</t>
+          <t>-8.2%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-23.6%</t>
+          <t>-23.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-4.6%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-328.7%</t>
+          <t>-329.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-151.7%</t>
+          <t>-150.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>94.1%</t>
+          <t>80.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2059</v>
+        <v>2060</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.5%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.6%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>85.2%</t>
+          <t>73.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>-16.7%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2062"/>
+  <dimension ref="A1:G2063"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48195,16 +48195,16 @@
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.307151357315617</v>
+        <v>-5.240885473559752</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.785890543235757</v>
+        <v>1.812396896738103</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.1934050180593213</v>
+        <v>0.1644018277749375</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.025150521311343</v>
+        <v>4.007748607140713</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.00570463184378</v>
+        <v>-4.939438748087914</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.913730116307027</v>
+        <v>1.940236469809374</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.4948517435311586</v>
+        <v>0.4658485532467748</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.213279439476982</v>
+        <v>4.195877525306352</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.030294876078964</v>
+        <v>-4.964028992323098</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.904865196365665</v>
+        <v>1.931371549868011</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.4948517435311586</v>
+        <v>0.4658485532467748</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.214250617229693</v>
+        <v>4.196848703059063</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.979256500072443</v>
+        <v>-4.912990616316578</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.926123451148028</v>
+        <v>1.952629804650374</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.4948517435311586</v>
+        <v>0.4658485532467748</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.215093521609448</v>
+        <v>4.197691607438817</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.938117205205812</v>
+        <v>-4.871851321449947</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.961617267968825</v>
+        <v>1.988123621471172</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.5359910383977894</v>
+        <v>0.5069878481134056</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.258815197403572</v>
+        <v>4.241413283232942</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.841482293187172</v>
+        <v>-4.775216409431307</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.816455228900216</v>
+        <v>1.842961582402562</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.6326259504164293</v>
+        <v>0.6036227601320455</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.13298014073869</v>
+        <v>4.11557822656806</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.972063027718015</v>
+        <v>-4.905797143962149</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.767724979161843</v>
+        <v>1.794231332664189</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.5020452158855868</v>
+        <v>0.473042025601203</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.058133744094149</v>
+        <v>4.040731829923518</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.807566693527053</v>
+        <v>-4.741300809771188</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.81795033191431</v>
+        <v>1.844456685416656</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.6665415500765487</v>
+        <v>0.6375383597921649</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.141258363684808</v>
+        <v>4.123856449514178</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.834936626211485</v>
+        <v>-4.76867074245562</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.806190069276967</v>
+        <v>1.832696422779313</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.6665415500765487</v>
+        <v>0.6375383597921649</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.140446074121238</v>
+        <v>4.123044159950608</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.845321821101375</v>
+        <v>-4.779055937345509</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.811904770446084</v>
+        <v>1.83841112394843</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.6561563551866594</v>
+        <v>0.6271531649022756</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.144083736312377</v>
+        <v>4.126681822141746</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.8639099798236</v>
+        <v>-4.797644096067734</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.875306512733619</v>
+        <v>1.901812866235965</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.637568196464434</v>
+        <v>0.6085650061800503</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.203767846855467</v>
+        <v>4.186365932684836</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.864208526519636</v>
+        <v>-4.79794264276377</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.872056104873503</v>
+        <v>1.898562458375849</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.6372696497683981</v>
+        <v>0.6082664594840144</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.200457729656144</v>
+        <v>4.183055815485513</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.763385392829208</v>
+        <v>-4.697119509073342</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.916916253289065</v>
+        <v>1.943422606791412</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.6497338652527519</v>
+        <v>0.6207306749683682</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.212467153886148</v>
+        <v>4.195065239715517</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.5726040320768</v>
+        <v>-4.506338148320935</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.993358051068572</v>
+        <v>2.019864404570918</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.8405152260051593</v>
+        <v>0.8115120357207756</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.327065223816135</v>
+        <v>4.309663309645504</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.55408717803498</v>
+        <v>-4.487821294279115</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.980601638422897</v>
+        <v>2.007107991925242</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.8534453554303675</v>
+        <v>0.8244421651459838</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.314660147208857</v>
+        <v>4.297258233038226</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.528893993533662</v>
+        <v>-4.462628109777797</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.025645848835482</v>
+        <v>2.052152202337828</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.8786385399316858</v>
+        <v>0.8496353496473021</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.364742994521706</v>
+        <v>4.347341080351075</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.516839866620699</v>
+        <v>-4.450573982864834</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.024154067502105</v>
+        <v>2.050660421004451</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.8906926668446487</v>
+        <v>0.861689476560265</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.365662038570921</v>
+        <v>4.348260124400291</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.523463113311057</v>
+        <v>-4.457197229555192</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.023385399010098</v>
+        <v>2.049891752512443</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.8840694201542902</v>
+        <v>0.8550662298699065</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.363568720740842</v>
+        <v>4.346166806570212</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.420582523782464</v>
+        <v>-4.3543166400266</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.077388660699417</v>
+        <v>2.103895014201763</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.9869500096828832</v>
+        <v>0.9579468193984995</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.43814810033588</v>
+        <v>4.42074618616525</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.444024562962551</v>
+        <v>-4.377758679206686</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.088214515200977</v>
+        <v>2.114720868703323</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.9869500096828832</v>
+        <v>0.9579468193984995</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.458350770509474</v>
+        <v>4.440948856338844</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.462097071254163</v>
+        <v>-4.395831187498298</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.080985511884332</v>
+        <v>2.107491865386678</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.9869500096828832</v>
+        <v>0.9579468193984995</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.458350770509474</v>
+        <v>4.440948856338844</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.693270865130795</v>
+        <v>-4.62700498137493</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.948767907927146</v>
+        <v>1.975274261429492</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.9869500096828832</v>
+        <v>0.9579468193984995</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.418602684102941</v>
+        <v>4.401200769932311</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.661984844590339</v>
+        <v>-4.595718960834475</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.968304935140268</v>
+        <v>1.994811288642614</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.018236030223338</v>
+        <v>0.9892328399389547</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.444396915424154</v>
+        <v>4.426995001253524</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.508959452477055</v>
+        <v>-4.44269356872119</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.128686091558486</v>
+        <v>2.155192445060831</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.171261422336622</v>
+        <v>1.142258232052239</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.635383150265029</v>
+        <v>4.617981236094399</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>4.120092521771348</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.537266766350325</v>
+        <v>-4.471000882594461</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.30482939091747</v>
+        <v>2.331335744419816</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.171261422336622</v>
+        <v>1.142258232052239</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.822849375173321</v>
+        <v>4.805447461002691</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>4.08949547312543</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.703859991463847</v>
+        <v>-4.637594107707983</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.207595052226144</v>
+        <v>2.234101405728489</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.0046681972231</v>
+        <v>0.9756650069387163</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.69229639145929</v>
+        <v>4.67489447728866</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>4.093171875787148</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.530795612081548</v>
+        <v>-4.464529728325683</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.280497206640781</v>
+        <v>2.307003560143127</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.0046681972231</v>
+        <v>0.9756650069387163</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.695972794121007</v>
+        <v>4.678570879950378</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>4.090789930910643</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.501549631625851</v>
+        <v>-4.435283747869986</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.289813653946555</v>
+        <v>2.316320007448901</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.0046681972231</v>
+        <v>0.9756650069387163</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.693590849244503</v>
+        <v>4.676188935073872</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>4.088083170068278</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.608475179503702</v>
+        <v>-4.542209295747837</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.244336673953049</v>
+        <v>2.270843027455395</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.8977426493452486</v>
+        <v>0.8687394590608649</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.626728759675427</v>
+        <v>4.609326845504797</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>4.089511972211512</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.753493738010951</v>
+        <v>-4.687227854255086</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.187758052693384</v>
+        <v>2.21426440619573</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.7527240908380001</v>
+        <v>0.7237209005536164</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.541146426714312</v>
+        <v>4.523744512543682</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>4.189443211469265</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.871835503795668</v>
+        <v>-4.805569620039804</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.24035258563725</v>
+        <v>2.266858939139596</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.7634101294008901</v>
+        <v>0.7344069391165065</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.647489289109799</v>
+        <v>4.630087374939169</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>4.187228908595204</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.923245926116376</v>
+        <v>-4.856980042360512</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.217574113834906</v>
+        <v>2.244080467337252</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.7634101294008901</v>
+        <v>0.7344069391165065</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.645274986235738</v>
+        <v>4.627873072065108</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>4.187132036669493</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.002665377324128</v>
+        <v>-4.936399493568263</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.185709461426095</v>
+        <v>2.212215814928441</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.7634101294008901</v>
+        <v>0.7344069391165065</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.645178114310028</v>
+        <v>4.627776200139397</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>4.187125930227537</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.098128375241346</v>
+        <v>-5.031862491485481</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.147518155817251</v>
+        <v>2.174024509319597</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.7634101294008901</v>
+        <v>0.7344069391165065</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.645172007868071</v>
+        <v>4.627770093697441</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,45 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.772338974041173</v>
+        <v>3.71539314550074</v>
       </c>
       <c r="C2062" t="n">
         <v>4.185222326790147</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.138148373285129</v>
+        <v>-5.033053074847404</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.129606553162348</v>
+        <v>2.171644672537438</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.7233901313571063</v>
+        <v>0.7332163557545831</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.619256405604411</v>
+        <v>4.625152140242897</v>
+      </c>
+    </row>
+    <row r="2063">
+      <c r="A2063" s="2" t="n">
+        <v>45525</v>
+      </c>
+      <c r="B2063" t="n">
+        <v>3.811886739566822</v>
+      </c>
+      <c r="C2063" t="n">
+        <v>4.300011853319528</v>
+      </c>
+      <c r="D2063" t="n">
+        <v>-5.033053074847404</v>
+      </c>
+      <c r="E2063" t="n">
+        <v>2.171644672537438</v>
+      </c>
+      <c r="F2063" t="n">
+        <v>0.7332163557545831</v>
+      </c>
+      <c r="G2063" t="n">
+        <v>4.293075650305895</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240821.xlsx
+++ b/tame_output/ON/bt/strategyON_20240821.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>57.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-11.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>49.3%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>97.9%</t>
+          <t>100.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>40.9%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>80.7%</t>
+          <t>82.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>118.4%</t>
+          <t>126.0%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.5%</t>
+          <t>-78.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.4%</t>
+          <t>107.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.2%</t>
+          <t>89.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.4%</t>
+          <t>-48.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.7%</t>
+          <t>-75.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.0%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-3.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-664.9%</t>
+          <t>-673.8%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.8%</t>
+          <t>-34.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-159.1%</t>
+          <t>-162.6%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>-11.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-23.5%</t>
+          <t>-23.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-4.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-329.0%</t>
+          <t>-328.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-150.7%</t>
+          <t>-149.3%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>80.8%</t>
+          <t>84.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-21.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>73.9%</t>
+          <t>76.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-9.1%</t>
         </is>
       </c>
     </row>
@@ -48195,16 +48195,16 @@
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.240885473559752</v>
+        <v>-5.330163591040062</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.812396896738103</v>
+        <v>1.776685649745978</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.1644018277749375</v>
+        <v>0.1778458071339445</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.007748607140713</v>
+        <v>4.015814994756117</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.939438748087914</v>
+        <v>-5.028716865568224</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.940236469809374</v>
+        <v>1.90452522281725</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.4658485532467748</v>
+        <v>0.4792925326057818</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.195877525306352</v>
+        <v>4.203943912921756</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.964028992323098</v>
+        <v>-5.053307109803408</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.931371549868011</v>
+        <v>1.895660302875886</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.4658485532467748</v>
+        <v>0.4792925326057818</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.196848703059063</v>
+        <v>4.204915090674467</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.912990616316578</v>
+        <v>-5.002268733796888</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.952629804650374</v>
+        <v>1.91691855765825</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.4658485532467748</v>
+        <v>0.4792925326057818</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.197691607438817</v>
+        <v>4.205757995054221</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.871851321449947</v>
+        <v>-4.961129438930257</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.988123621471172</v>
+        <v>1.952412374479048</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.5069878481134056</v>
+        <v>0.5204318274724126</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.241413283232942</v>
+        <v>4.249479670848346</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.775216409431307</v>
+        <v>-4.864494526911617</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.842961582402562</v>
+        <v>1.807250335410438</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.6036227601320455</v>
+        <v>0.6170667394910525</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.11557822656806</v>
+        <v>4.123644614183464</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.905797143962149</v>
+        <v>-4.99507526144246</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.794231332664189</v>
+        <v>1.758520085672065</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.473042025601203</v>
+        <v>0.48648600496021</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.040731829923518</v>
+        <v>4.048798217538923</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.741300809771188</v>
+        <v>-4.830578927251498</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.844456685416656</v>
+        <v>1.808745438424532</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.6375383597921649</v>
+        <v>0.6509823391511719</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.123856449514178</v>
+        <v>4.131922837129582</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.76867074245562</v>
+        <v>-4.85794885993593</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.832696422779313</v>
+        <v>1.796985175787189</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.6375383597921649</v>
+        <v>0.6509823391511719</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.123044159950608</v>
+        <v>4.131110547566012</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.779055937345509</v>
+        <v>-4.868334054825819</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.83841112394843</v>
+        <v>1.802699876956306</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.6271531649022756</v>
+        <v>0.6405971442612826</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.126681822141746</v>
+        <v>4.13474820975715</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.797644096067734</v>
+        <v>-4.886922213548044</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.901812866235965</v>
+        <v>1.866101619243841</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.6085650061800503</v>
+        <v>0.6220089855390571</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.186365932684836</v>
+        <v>4.19443232030024</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.79794264276377</v>
+        <v>-4.88722076024408</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.898562458375849</v>
+        <v>1.862851211383725</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.6082664594840144</v>
+        <v>0.6217104388430212</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.183055815485513</v>
+        <v>4.191122203100917</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.697119509073342</v>
+        <v>-4.786397626553653</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.943422606791412</v>
+        <v>1.907711359799288</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.6207306749683682</v>
+        <v>0.6341746543273751</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.195065239715517</v>
+        <v>4.203131627330921</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.506338148320935</v>
+        <v>-4.595616265801246</v>
       </c>
       <c r="E2041" t="n">
-        <v>2.019864404570918</v>
+        <v>1.984153157578794</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.8115120357207756</v>
+        <v>0.8249560150797824</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.309663309645504</v>
+        <v>4.317729697260908</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.487821294279115</v>
+        <v>-4.577099411759425</v>
       </c>
       <c r="E2042" t="n">
-        <v>2.007107991925242</v>
+        <v>1.971396744933118</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.8244421651459838</v>
+        <v>0.8378861445049907</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.297258233038226</v>
+        <v>4.30532462065363</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.462628109777797</v>
+        <v>-4.551906227258107</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.052152202337828</v>
+        <v>2.016440955345704</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.8496353496473021</v>
+        <v>0.863079329006309</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.347341080351075</v>
+        <v>4.355407467966479</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.450573982864834</v>
+        <v>-4.539852100345144</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.050660421004451</v>
+        <v>2.014949174012327</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.861689476560265</v>
+        <v>0.8751334559192718</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.348260124400291</v>
+        <v>4.356326512015695</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.457197229555192</v>
+        <v>-4.546475347035503</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.049891752512443</v>
+        <v>2.014180505520319</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.8550662298699065</v>
+        <v>0.8685102092289134</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.346166806570212</v>
+        <v>4.354233194185616</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.3543166400266</v>
+        <v>-4.44359475750691</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.103895014201763</v>
+        <v>2.068183767209639</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.9579468193984995</v>
+        <v>0.9713907987575063</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.42074618616525</v>
+        <v>4.428812573780654</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.377758679206686</v>
+        <v>-4.467036796686997</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.114720868703323</v>
+        <v>2.079009621711198</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.9579468193984995</v>
+        <v>0.9713907987575063</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.440948856338844</v>
+        <v>4.449015243954248</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.395831187498298</v>
+        <v>-4.485109304978608</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.107491865386678</v>
+        <v>2.071780618394554</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.9579468193984995</v>
+        <v>0.9713907987575063</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.440948856338844</v>
+        <v>4.449015243954248</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.62700498137493</v>
+        <v>-4.71628309885524</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.975274261429492</v>
+        <v>1.939563014437367</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.9579468193984995</v>
+        <v>0.9713907987575063</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.401200769932311</v>
+        <v>4.409267157547715</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.595718960834475</v>
+        <v>-4.684997078314785</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.994811288642614</v>
+        <v>1.95910004165049</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.9892328399389547</v>
+        <v>1.002676819297962</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.426995001253524</v>
+        <v>4.435061388868928</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.44269356872119</v>
+        <v>-4.5319716862015</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.155192445060831</v>
+        <v>2.119481198068708</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.142258232052239</v>
+        <v>1.155702211411246</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.617981236094399</v>
+        <v>4.626047623709803</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>4.120092521771348</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.471000882594461</v>
+        <v>-4.560279000074771</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.331335744419816</v>
+        <v>2.295624497427692</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.142258232052239</v>
+        <v>1.155702211411246</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.805447461002691</v>
+        <v>4.813513848618095</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>4.08949547312543</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.637594107707983</v>
+        <v>-4.726872225188293</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.234101405728489</v>
+        <v>2.198390158736365</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.9756650069387163</v>
+        <v>0.9891089862977231</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.67489447728866</v>
+        <v>4.682960864904064</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>4.093171875787148</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.464529728325683</v>
+        <v>-4.553807845805993</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.307003560143127</v>
+        <v>2.271292313151003</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.9756650069387163</v>
+        <v>0.9891089862977231</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.678570879950378</v>
+        <v>4.686637267565782</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>4.090789930910643</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.435283747869986</v>
+        <v>-4.524561865350297</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.316320007448901</v>
+        <v>2.280608760456777</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.9756650069387163</v>
+        <v>0.9891089862977231</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.676188935073872</v>
+        <v>4.684255322689276</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>4.088083170068278</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.542209295747837</v>
+        <v>-4.631487413228148</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.270843027455395</v>
+        <v>2.235131780463272</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.8687394590608649</v>
+        <v>0.8821834384198718</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.609326845504797</v>
+        <v>4.617393233120201</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>4.089511972211512</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.687227854255086</v>
+        <v>-4.776505971735396</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.21426440619573</v>
+        <v>2.178553159203606</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.7237209005536164</v>
+        <v>0.7371648799126232</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.523744512543682</v>
+        <v>4.531810900159086</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>4.189443211469265</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.805569620039804</v>
+        <v>-4.894847737520114</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.266858939139596</v>
+        <v>2.231147692147472</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.7344069391165065</v>
+        <v>0.7478509184755133</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.630087374939169</v>
+        <v>4.638153762554573</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>4.187228908595204</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.856980042360512</v>
+        <v>-4.946258159840822</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.244080467337252</v>
+        <v>2.208369220345128</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.7344069391165065</v>
+        <v>0.7478509184755133</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.627873072065108</v>
+        <v>4.635939459680512</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>4.187132036669493</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.936399493568263</v>
+        <v>-5.025677611048573</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.212215814928441</v>
+        <v>2.176504567936317</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.7344069391165065</v>
+        <v>0.7478509184755133</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.627776200139397</v>
+        <v>4.635842587754802</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>4.187125930227537</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.031862491485481</v>
+        <v>-5.121140608965791</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.174024509319597</v>
+        <v>2.138313262327473</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.7344069391165065</v>
+        <v>0.7478509184755133</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.627770093697441</v>
+        <v>4.635836481312845</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>4.185222326790147</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.033053074847404</v>
+        <v>-5.122331192327715</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.171644672537438</v>
+        <v>2.135933425545314</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.7332163557545831</v>
+        <v>0.74666033511359</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.625152140242897</v>
+        <v>4.633218527858301</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.811886739566822</v>
+        <v>3.773586166404313</v>
       </c>
       <c r="C2063" t="n">
-        <v>4.300011853319528</v>
+        <v>4.375823822464037</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.033053074847404</v>
+        <v>-5.122331192327715</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.171644672537438</v>
+        <v>2.135933425545314</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.7332163557545831</v>
+        <v>0.74666033511359</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.293075650305895</v>
+        <v>4.368887619450405</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240821.xlsx
+++ b/tame_output/ON/bt/strategyON_20240821.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.4%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>49.3%</t>
+          <t>55.0%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>100.2%</t>
+          <t>98.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>40.9%</t>
+          <t>40.1%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>82.9%</t>
+          <t>80.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>126.0%</t>
+          <t>119.6%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.8%</t>
+          <t>-78.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.2%</t>
+          <t>107.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.4%</t>
+          <t>123.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-39.8%</t>
+          <t>-42.4%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.7%</t>
+          <t>-48.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.1%</t>
+          <t>-74.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>88.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>430.6%</t>
+          <t>430.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-3.0%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-673.8%</t>
+          <t>-666.8%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.1%</t>
+          <t>-33.8%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-162.6%</t>
+          <t>-159.8%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-11.1%</t>
+          <t>-10.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-8.2%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>-3.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-328.8%</t>
+          <t>-329.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-149.3%</t>
+          <t>-148.1%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>84.2%</t>
+          <t>81.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.0%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.6%</t>
+          <t>-20.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>76.5%</t>
+          <t>74.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-9.1%</t>
+          <t>-15.5%</t>
         </is>
       </c>
     </row>
@@ -47827,16 +47827,16 @@
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.567492280613894</v>
+        <v>-3.48203298395245</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.039527271762863</v>
+        <v>2.073710990427441</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.7821373141412601</v>
+        <v>0.817873696178675</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.936162996806924</v>
+        <v>3.957604826029374</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.595393067723367</v>
+        <v>-3.509933771061923</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.026890998046076</v>
+        <v>2.061074716710654</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.7475403899983253</v>
+        <v>0.7832767720357402</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.913928883448166</v>
+        <v>3.935370712670615</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.717919170426261</v>
+        <v>-3.632459873764817</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.974645000942117</v>
+        <v>2.008828719606695</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.6250142872954314</v>
+        <v>0.6607506693328463</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.837177665803628</v>
+        <v>3.858619495026077</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.94843366661185</v>
+        <v>-3.862974369950406</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.949145162058386</v>
+        <v>1.983328880722963</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.3944997911098427</v>
+        <v>0.4302361731472576</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.765574927682779</v>
+        <v>3.787016756905228</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.205154484606673</v>
+        <v>-4.119695187945229</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.986768553862303</v>
+        <v>2.020952272526881</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.2860852169660278</v>
+        <v>0.3218215990034428</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.840837902198337</v>
+        <v>3.862279731420786</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.359140902382814</v>
+        <v>-4.27368160572137</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.994154255897487</v>
+        <v>2.028337974562064</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.2860852169660278</v>
+        <v>0.3218215990034428</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.909818171343977</v>
+        <v>3.931260000566426</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.308618998555148</v>
+        <v>-4.223159701893704</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.000414219548674</v>
+        <v>2.034597938213252</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.2860852169660278</v>
+        <v>0.3218215990034428</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.895869373464098</v>
+        <v>3.917311202686546</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.561094152562872</v>
+        <v>-4.475634855901428</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.911294647000998</v>
+        <v>1.945478365665576</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.2860852169660278</v>
+        <v>0.3218215990034428</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.907739862519512</v>
+        <v>3.92918169174196</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.853989909042284</v>
+        <v>-4.76853061238084</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.795346878928177</v>
+        <v>1.829530597592755</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.2860852169660278</v>
+        <v>0.3218215990034428</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.908950397038455</v>
+        <v>3.930392226260905</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.040654037177092</v>
+        <v>-4.955194740515648</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.724802969901575</v>
+        <v>1.758986688566153</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.259346246141468</v>
+        <v>0.2950826281788829</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.897028756771041</v>
+        <v>3.918470585993489</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.186674724091055</v>
+        <v>-5.101215427429611</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.66147254787218</v>
+        <v>1.695656266536758</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.250263154347611</v>
+        <v>0.2859995363850259</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.886656754430916</v>
+        <v>3.908098583653365</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.278388733200639</v>
+        <v>-5.192929436539195</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.78699100092739</v>
+        <v>1.821174719591968</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.250263154347611</v>
+        <v>0.2859995363850259</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.04886081112996</v>
+        <v>4.070302640352409</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.310040392260609</v>
+        <v>-5.224581095599165</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.769176975267217</v>
+        <v>1.803360693931794</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.2450946971031708</v>
+        <v>0.2808310791405857</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.04060637474711</v>
+        <v>4.062048203969559</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.391975210529492</v>
+        <v>-5.306515913868048</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.746632465528155</v>
+        <v>1.780816184192732</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.2351599515160906</v>
+        <v>0.2708963335535055</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.044874944963353</v>
+        <v>4.066316774185802</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.493951332777899</v>
+        <v>-5.408492036116455</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.714767655084694</v>
+        <v>1.748951373749271</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.133183829267683</v>
+        <v>0.1689202113050979</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.992614910070211</v>
+        <v>4.01405673929266</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.383945049300678</v>
+        <v>-5.298485752639234</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.750923055719758</v>
+        <v>1.785106774384336</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.1563884011849582</v>
+        <v>0.1921247832223731</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.998690540464752</v>
+        <v>4.0201323696872</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.330163591040062</v>
+        <v>-5.221692060654173</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.776685649745978</v>
+        <v>1.820074261900334</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.1778458071339445</v>
+        <v>0.2291414000967362</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.015814994756117</v>
+        <v>4.046592350533793</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.028716865568224</v>
+        <v>-4.920245335182336</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.90452522281725</v>
+        <v>1.947913834971605</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.4792925326057818</v>
+        <v>0.5305881255685735</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.203943912921756</v>
+        <v>4.234721268699431</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.053307109803408</v>
+        <v>-4.94483557941752</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.895660302875886</v>
+        <v>1.939048915030242</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.4792925326057818</v>
+        <v>0.5305881255685735</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.204915090674467</v>
+        <v>4.235692446452141</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.002268733796888</v>
+        <v>-4.893797203410999</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.91691855765825</v>
+        <v>1.960307169812605</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.4792925326057818</v>
+        <v>0.5305881255685735</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.205757995054221</v>
+        <v>4.236535350831897</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.961129438930257</v>
+        <v>-4.852657908544368</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.952412374479048</v>
+        <v>1.995800986633403</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.5204318274724126</v>
+        <v>0.5717274204352043</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.249479670848346</v>
+        <v>4.28025702662602</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.864494526911617</v>
+        <v>-4.756022996525728</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.807250335410438</v>
+        <v>1.850638947564794</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.6170667394910525</v>
+        <v>0.6683623324538442</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.123644614183464</v>
+        <v>4.154421969961139</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.99507526144246</v>
+        <v>-4.886603731056571</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.758520085672065</v>
+        <v>1.80190869782642</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.48648600496021</v>
+        <v>0.5377815979230017</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.048798217538923</v>
+        <v>4.079575573316597</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.830578927251498</v>
+        <v>-4.722107396865609</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.808745438424532</v>
+        <v>1.852134050578888</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.6509823391511719</v>
+        <v>0.7022779321139636</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.131922837129582</v>
+        <v>4.162700192907257</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.85794885993593</v>
+        <v>-4.749477329550041</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.796985175787189</v>
+        <v>1.840373787941544</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.6509823391511719</v>
+        <v>0.7022779321139636</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.131110547566012</v>
+        <v>4.161887903343687</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.868334054825819</v>
+        <v>-4.759862524439931</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.802699876956306</v>
+        <v>1.846088489110661</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.6405971442612826</v>
+        <v>0.6918927372240743</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.13474820975715</v>
+        <v>4.165525565534826</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.886922213548044</v>
+        <v>-4.778450683162156</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.866101619243841</v>
+        <v>1.909490231398197</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.6220089855390571</v>
+        <v>0.673304578501849</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.19443232030024</v>
+        <v>4.225209676077916</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.88722076024408</v>
+        <v>-4.778749229858192</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.862851211383725</v>
+        <v>1.906239823538081</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.6217104388430212</v>
+        <v>0.6730060318058131</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.191122203100917</v>
+        <v>4.221899558878593</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.786397626553653</v>
+        <v>-4.677926096167764</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.907711359799288</v>
+        <v>1.951099971953643</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.6341746543273751</v>
+        <v>0.6854702472901669</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.203131627330921</v>
+        <v>4.233908983108596</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.595616265801246</v>
+        <v>-4.487144735415356</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.984153157578794</v>
+        <v>2.027541769733149</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.8249560150797824</v>
+        <v>0.8762516080425743</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.317729697260908</v>
+        <v>4.348507053038584</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.577099411759425</v>
+        <v>-4.468627881373536</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.971396744933118</v>
+        <v>2.014785357087474</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.8378861445049907</v>
+        <v>0.8891817374677825</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.30532462065363</v>
+        <v>4.336101976431306</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.551906227258107</v>
+        <v>-4.443434696872218</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.016440955345704</v>
+        <v>2.05982956750006</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.863079329006309</v>
+        <v>0.9143749219691009</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.355407467966479</v>
+        <v>4.386184823744155</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.539852100345144</v>
+        <v>-4.431380569959255</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.014949174012327</v>
+        <v>2.058337786166683</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.8751334559192718</v>
+        <v>0.9264290488820637</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.356326512015695</v>
+        <v>4.38710386779337</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.546475347035503</v>
+        <v>-4.438003816649613</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.014180505520319</v>
+        <v>2.057569117674675</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.8685102092289134</v>
+        <v>0.9198058021917053</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.354233194185616</v>
+        <v>4.385010549963291</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.44359475750691</v>
+        <v>-4.33512322712102</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.068183767209639</v>
+        <v>2.111572379363995</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.9713907987575063</v>
+        <v>1.022686391720298</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.428812573780654</v>
+        <v>4.459589929558329</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760317</v>
+        <v>3.646857607760316</v>
       </c>
       <c r="C2047" t="n">
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.467036796686997</v>
+        <v>-4.358565266301107</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.079009621711198</v>
+        <v>2.122398233865554</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.9713907987575063</v>
+        <v>1.022686391720298</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.449015243954248</v>
+        <v>4.479792599731923</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781708</v>
+        <v>3.666767386781707</v>
       </c>
       <c r="C2048" t="n">
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.485109304978608</v>
+        <v>-4.376637774592719</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.071780618394554</v>
+        <v>2.11516923054891</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.9713907987575063</v>
+        <v>1.022686391720298</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.449015243954248</v>
+        <v>4.479792599731923</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082837</v>
+        <v>3.670068888082836</v>
       </c>
       <c r="C2049" t="n">
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.71628309885524</v>
+        <v>-4.607811568469351</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.939563014437367</v>
+        <v>1.982951626591723</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.9713907987575063</v>
+        <v>1.022686391720298</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.409267157547715</v>
+        <v>4.440044513325391</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943589</v>
+        <v>3.745593333943587</v>
       </c>
       <c r="C2050" t="n">
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.684997078314785</v>
+        <v>-4.576525547928895</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.95910004165049</v>
+        <v>2.002488653804845</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.002676819297962</v>
+        <v>1.053972412260753</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.435061388868928</v>
+        <v>4.465838744646604</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677827</v>
+        <v>3.730590658677825</v>
       </c>
       <c r="C2051" t="n">
         <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.5319716862015</v>
+        <v>-4.423500155815611</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.119481198068708</v>
+        <v>2.162869810223063</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.155702211411246</v>
+        <v>1.206997804374037</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.626047623709803</v>
+        <v>4.656824979487478</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073886</v>
+        <v>3.741298518073885</v>
       </c>
       <c r="C2052" t="n">
         <v>4.120092521771348</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.560279000074771</v>
+        <v>-4.451807469688881</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.295624497427692</v>
+        <v>2.339013109582048</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.155702211411246</v>
+        <v>1.206997804374037</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.813513848618095</v>
+        <v>4.844291204395771</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699135800903171</v>
+        <v>3.69913580090317</v>
       </c>
       <c r="C2053" t="n">
         <v>4.08949547312543</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.726872225188293</v>
+        <v>-4.618400694802403</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.198390158736365</v>
+        <v>2.241778770890721</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.9891089862977231</v>
+        <v>1.040404579260515</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.682960864904064</v>
+        <v>4.713738220681739</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568386</v>
+        <v>3.708202704568384</v>
       </c>
       <c r="C2054" t="n">
         <v>4.093171875787148</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.553807845805993</v>
+        <v>-4.445336315420104</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.271292313151003</v>
+        <v>2.314680925305359</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.9891089862977231</v>
+        <v>1.040404579260515</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.686637267565782</v>
+        <v>4.717414623343457</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740601586682208</v>
+        <v>3.740601586682206</v>
       </c>
       <c r="C2055" t="n">
         <v>4.090789930910643</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.524561865350297</v>
+        <v>-4.416090334964407</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.280608760456777</v>
+        <v>2.323997372611132</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.9891089862977231</v>
+        <v>1.040404579260515</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.684255322689276</v>
+        <v>4.715032678466952</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539111</v>
+        <v>3.699424827539109</v>
       </c>
       <c r="C2056" t="n">
         <v>4.088083170068278</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.631487413228148</v>
+        <v>-4.523015882842258</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.235131780463272</v>
+        <v>2.278520392617628</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.8821834384198718</v>
+        <v>0.9334790313826636</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.617393233120201</v>
+        <v>4.648170588897877</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983741</v>
+        <v>3.689962785983739</v>
       </c>
       <c r="C2057" t="n">
         <v>4.089511972211512</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.776505971735396</v>
+        <v>-4.668034441349507</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.178553159203606</v>
+        <v>2.221941771357962</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.7371648799126232</v>
+        <v>0.7884604728754151</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.531810900159086</v>
+        <v>4.562588255936761</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711872614969752</v>
+        <v>3.71187261496975</v>
       </c>
       <c r="C2058" t="n">
         <v>4.189443211469265</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.894847737520114</v>
+        <v>-4.786376207134224</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.231147692147472</v>
+        <v>2.274536304301828</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.7478509184755133</v>
+        <v>0.7991465114383052</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.638153762554573</v>
+        <v>4.668931118332249</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714899237073542</v>
+        <v>3.71489923707354</v>
       </c>
       <c r="C2059" t="n">
         <v>4.187228908595204</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.946258159840822</v>
+        <v>-4.837786629454932</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.208369220345128</v>
+        <v>2.251757832499484</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.7478509184755133</v>
+        <v>0.7991465114383052</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.635939459680512</v>
+        <v>4.666716815458187</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704778134720069</v>
+        <v>3.704778134720067</v>
       </c>
       <c r="C2060" t="n">
         <v>4.187132036669493</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.025677611048573</v>
+        <v>-4.917206080662684</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.176504567936317</v>
+        <v>2.219893180090672</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.7478509184755133</v>
+        <v>0.7991465114383052</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.635842587754802</v>
+        <v>4.666619943532477</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736825137581136</v>
+        <v>3.736825137581135</v>
       </c>
       <c r="C2061" t="n">
         <v>4.187125930227537</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.121140608965791</v>
+        <v>-5.012669078579902</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.138313262327473</v>
+        <v>2.181701874481829</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.7478509184755133</v>
+        <v>0.7991465114383052</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.635836481312845</v>
+        <v>4.66661383709052</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.71539314550074</v>
+        <v>3.715393145500737</v>
       </c>
       <c r="C2062" t="n">
         <v>4.185222326790147</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.122331192327715</v>
+        <v>-5.052689076623685</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.135933425545314</v>
+        <v>2.163790271826926</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.74666033511359</v>
+        <v>0.7591265133945213</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.633218527858301</v>
+        <v>4.640698234826861</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.773586166404313</v>
+        <v>3.831171972203367</v>
       </c>
       <c r="C2063" t="n">
-        <v>4.375823822464037</v>
+        <v>4.312399423030092</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.122331192327715</v>
+        <v>-5.052689076623685</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.135933425545314</v>
+        <v>2.163790271826926</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.74666033511359</v>
+        <v>0.7591265133945213</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.368887619450405</v>
+        <v>4.30546322001646</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240821.xlsx
+++ b/tame_output/ON/bt/strategyON_20240821.xlsx
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.5%</t>
+          <t>-78.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.1%</t>
+          <t>107.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.9%</t>
+          <t>90.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.4%</t>
+          <t>-48.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.7%</t>
+          <t>-74.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>88.7%</t>
+          <t>88.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-3.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-666.8%</t>
+          <t>-659.5%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24.9%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.8%</t>
+          <t>-33.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-159.8%</t>
+          <t>-156.9%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-10.8%</t>
+          <t>-11.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-7.5%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-23.4%</t>
+          <t>-23.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-329.5%</t>
+          <t>-330.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-148.1%</t>
+          <t>-151.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>81.2%</t>
+          <t>81.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.4%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-20.0%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>74.5%</t>
+          <t>74.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -47821,16 +47821,16 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378394</v>
+        <v>3.749882691378393</v>
       </c>
       <c r="C2012" t="n">
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.48203298395245</v>
+        <v>-3.474771441078031</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.073710990427441</v>
+        <v>2.076615607577208</v>
       </c>
       <c r="F2012" t="n">
         <v>0.817873696178675</v>
@@ -47844,16 +47844,16 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006977</v>
+        <v>3.715819895006976</v>
       </c>
       <c r="C2013" t="n">
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.509933771061923</v>
+        <v>-3.502672228187504</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.061074716710654</v>
+        <v>2.063979333860422</v>
       </c>
       <c r="F2013" t="n">
         <v>0.7832767720357402</v>
@@ -47867,16 +47867,16 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787388</v>
+        <v>3.684895778787387</v>
       </c>
       <c r="C2014" t="n">
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.632459873764817</v>
+        <v>-3.625198330890398</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.008828719606695</v>
+        <v>2.011733336756463</v>
       </c>
       <c r="F2014" t="n">
         <v>0.6607506693328463</v>
@@ -47890,16 +47890,16 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585939</v>
+        <v>3.619348081585938</v>
       </c>
       <c r="C2015" t="n">
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.862974369950406</v>
+        <v>-3.855712827075987</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.983328880722963</v>
+        <v>1.986233497872731</v>
       </c>
       <c r="F2015" t="n">
         <v>0.4302361731472576</v>
@@ -47913,16 +47913,16 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814666</v>
+        <v>3.640750087814665</v>
       </c>
       <c r="C2016" t="n">
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.119695187945229</v>
+        <v>-4.11243364507081</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.020952272526881</v>
+        <v>2.023856889676648</v>
       </c>
       <c r="F2016" t="n">
         <v>0.3218215990034428</v>
@@ -47936,16 +47936,16 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237095</v>
+        <v>3.668289004237094</v>
       </c>
       <c r="C2017" t="n">
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.27368160572137</v>
+        <v>-4.266420062846951</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.028337974562064</v>
+        <v>2.031242591711832</v>
       </c>
       <c r="F2017" t="n">
         <v>0.3218215990034428</v>
@@ -47959,16 +47959,16 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423388</v>
+        <v>3.619923016423387</v>
       </c>
       <c r="C2018" t="n">
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.223159701893704</v>
+        <v>-4.215898159019285</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.034597938213252</v>
+        <v>2.037502555363019</v>
       </c>
       <c r="F2018" t="n">
         <v>0.3218215990034428</v>
@@ -47982,16 +47982,16 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609754</v>
+        <v>3.656332733609753</v>
       </c>
       <c r="C2019" t="n">
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.475634855901428</v>
+        <v>-4.468373313027009</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.945478365665576</v>
+        <v>1.948382982815343</v>
       </c>
       <c r="F2019" t="n">
         <v>0.3218215990034428</v>
@@ -48005,16 +48005,16 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973159</v>
+        <v>3.674028535973158</v>
       </c>
       <c r="C2020" t="n">
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.76853061238084</v>
+        <v>-4.761269069506421</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.829530597592755</v>
+        <v>1.832435214742522</v>
       </c>
       <c r="F2020" t="n">
         <v>0.3218215990034428</v>
@@ -48028,16 +48028,16 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251947</v>
+        <v>3.663509457251946</v>
       </c>
       <c r="C2021" t="n">
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.955194740515648</v>
+        <v>-4.94793319764123</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.758986688566153</v>
+        <v>1.761891305715921</v>
       </c>
       <c r="F2021" t="n">
         <v>0.2950826281788829</v>
@@ -48051,16 +48051,16 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916203</v>
+        <v>3.652149152916202</v>
       </c>
       <c r="C2022" t="n">
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.101215427429611</v>
+        <v>-5.093953884555192</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.695656266536758</v>
+        <v>1.698560883686525</v>
       </c>
       <c r="F2022" t="n">
         <v>0.2859995363850259</v>
@@ -48074,16 +48074,16 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.66796230683033</v>
+        <v>3.667962306830329</v>
       </c>
       <c r="C2023" t="n">
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.192929436539195</v>
+        <v>-5.185667893664776</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.821174719591968</v>
+        <v>1.824079336741736</v>
       </c>
       <c r="F2023" t="n">
         <v>0.2859995363850259</v>
@@ -48097,16 +48097,16 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071552</v>
+        <v>3.696539468071551</v>
       </c>
       <c r="C2024" t="n">
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.224581095599165</v>
+        <v>-5.217319552724746</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.803360693931794</v>
+        <v>1.806265311081562</v>
       </c>
       <c r="F2024" t="n">
         <v>0.2808310791405857</v>
@@ -48120,16 +48120,16 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868147</v>
+        <v>3.750044015868145</v>
       </c>
       <c r="C2025" t="n">
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.306515913868048</v>
+        <v>-5.299254370993629</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.780816184192732</v>
+        <v>1.7837208013425</v>
       </c>
       <c r="F2025" t="n">
         <v>0.2708963335535055</v>
@@ -48143,16 +48143,16 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332692</v>
+        <v>3.78363286733269</v>
       </c>
       <c r="C2026" t="n">
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.408492036116455</v>
+        <v>-5.401230493242037</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.748951373749271</v>
+        <v>1.751855990899039</v>
       </c>
       <c r="F2026" t="n">
         <v>0.1689202113050979</v>
@@ -48166,16 +48166,16 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231809</v>
+        <v>3.798296784231807</v>
       </c>
       <c r="C2027" t="n">
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.298485752639234</v>
+        <v>-5.291224209764815</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.785106774384336</v>
+        <v>1.788011391534103</v>
       </c>
       <c r="F2027" t="n">
         <v>0.1921247832223731</v>
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818524</v>
+        <v>3.785563924818522</v>
       </c>
       <c r="C2028" t="n">
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.221692060654173</v>
+        <v>-5.148164634023889</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.820074261900334</v>
+        <v>1.849485232552448</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.2291414000967362</v>
+        <v>0.2001382098123524</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.046592350533793</v>
+        <v>4.029190436363162</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.77723741205179</v>
+        <v>3.777237412051788</v>
       </c>
       <c r="C2029" t="n">
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.920245335182336</v>
+        <v>-4.846717908552051</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.947913834971605</v>
+        <v>1.977324805623719</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.5305881255685735</v>
+        <v>0.5015849352841897</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.234721268699431</v>
+        <v>4.217319354528801</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679626</v>
+        <v>3.812635940679624</v>
       </c>
       <c r="C2030" t="n">
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.94483557941752</v>
+        <v>-4.871308152787235</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.939048915030242</v>
+        <v>1.968459885682356</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.5305881255685735</v>
+        <v>0.5015849352841897</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.235692446452141</v>
+        <v>4.218290532281511</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474161</v>
+        <v>3.821184182474159</v>
       </c>
       <c r="C2031" t="n">
         <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.893797203410999</v>
+        <v>-4.820269776780715</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.960307169812605</v>
+        <v>1.989718140464719</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.5305881255685735</v>
+        <v>0.5015849352841897</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.236535350831897</v>
+        <v>4.219133436661267</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969544</v>
+        <v>3.831734516969543</v>
       </c>
       <c r="C2032" t="n">
         <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.852657908544368</v>
+        <v>-4.779130481914084</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.995800986633403</v>
+        <v>2.025211957285517</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.5717274204352043</v>
+        <v>0.5427242301508205</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.28025702662602</v>
+        <v>4.26285511245539</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.82575293270048</v>
+        <v>3.825752932700478</v>
       </c>
       <c r="C2033" t="n">
         <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.756022996525728</v>
+        <v>-4.682495569895444</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.850638947564794</v>
+        <v>1.880049918216907</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.6683623324538442</v>
+        <v>0.6393591421694604</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.154421969961139</v>
+        <v>4.137020055790509</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077641</v>
+        <v>3.804688961077639</v>
       </c>
       <c r="C2034" t="n">
         <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.886603731056571</v>
+        <v>-4.813076304426287</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.80190869782642</v>
+        <v>1.831319668478534</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.5377815979230017</v>
+        <v>0.5087784076386179</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.079575573316597</v>
+        <v>4.062173659145967</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833459</v>
+        <v>3.775028860833457</v>
       </c>
       <c r="C2035" t="n">
         <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.722107396865609</v>
+        <v>-4.648579970235325</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.852134050578888</v>
+        <v>1.881545021231001</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.7022779321139636</v>
+        <v>0.6732747418295798</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.162700192907257</v>
+        <v>4.145298278736627</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077629</v>
+        <v>3.821030660077628</v>
       </c>
       <c r="C2036" t="n">
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.749477329550041</v>
+        <v>-4.675949902919757</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.840373787941544</v>
+        <v>1.869784758593658</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.7022779321139636</v>
+        <v>0.6732747418295798</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.161887903343687</v>
+        <v>4.144485989173057</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.83230702414791</v>
+        <v>3.832307024147909</v>
       </c>
       <c r="C2037" t="n">
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.759862524439931</v>
+        <v>-4.686335097809646</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.846088489110661</v>
+        <v>1.875499459762775</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.6918927372240743</v>
+        <v>0.6628895469396905</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.165525565534826</v>
+        <v>4.148123651364195</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735282</v>
+        <v>3.83441549373528</v>
       </c>
       <c r="C2038" t="n">
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.778450683162156</v>
+        <v>-4.704923256531871</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.909490231398197</v>
+        <v>1.93890120205031</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.673304578501849</v>
+        <v>0.6443013882174651</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.225209676077916</v>
+        <v>4.207807761907286</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496555</v>
+        <v>3.855120535496553</v>
       </c>
       <c r="C2039" t="n">
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.778749229858192</v>
+        <v>-4.705221803227907</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.906239823538081</v>
+        <v>1.935650794190194</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.6730060318058131</v>
+        <v>0.6440028415214292</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.221899558878593</v>
+        <v>4.204497644707963</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108857</v>
+        <v>3.815643212108855</v>
       </c>
       <c r="C2040" t="n">
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.677926096167764</v>
+        <v>-4.604398669537479</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.951099971953643</v>
+        <v>1.980510942605757</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.6854702472901669</v>
+        <v>0.656467057005783</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.233908983108596</v>
+        <v>4.216507068937966</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121466</v>
+        <v>3.807356168121465</v>
       </c>
       <c r="C2041" t="n">
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.487144735415356</v>
+        <v>-4.413617308785073</v>
       </c>
       <c r="E2041" t="n">
-        <v>2.027541769733149</v>
+        <v>2.056952740385263</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.8762516080425743</v>
+        <v>0.8472484177581904</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.348507053038584</v>
+        <v>4.331105138867954</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.77523303390608</v>
+        <v>3.775233033906078</v>
       </c>
       <c r="C2042" t="n">
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.468627881373536</v>
+        <v>-4.395100454743252</v>
       </c>
       <c r="E2042" t="n">
-        <v>2.014785357087474</v>
+        <v>2.044196327739588</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.8891817374677825</v>
+        <v>0.8601785471833986</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.336101976431306</v>
+        <v>4.318700062260675</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912985</v>
+        <v>3.785761685912983</v>
       </c>
       <c r="C2043" t="n">
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.443434696872218</v>
+        <v>-4.369907270241934</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.05982956750006</v>
+        <v>2.089240538152173</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.9143749219691009</v>
+        <v>0.8853717316847169</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.386184823744155</v>
+        <v>4.368782909573524</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539894</v>
+        <v>3.743767956539893</v>
       </c>
       <c r="C2044" t="n">
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.431380569959255</v>
+        <v>-4.357853143328971</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.058337786166683</v>
+        <v>2.087748756818796</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.9264290488820637</v>
+        <v>0.8974258585976798</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.38710386779337</v>
+        <v>4.36970195362274</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811009</v>
+        <v>3.725010844811007</v>
       </c>
       <c r="C2045" t="n">
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.438003816649613</v>
+        <v>-4.36447639001933</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.057569117674675</v>
+        <v>2.086980088326789</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.9198058021917053</v>
+        <v>0.8908026119073214</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.385010549963291</v>
+        <v>4.367608635792661</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.61232244438292</v>
+        <v>3.612322444382918</v>
       </c>
       <c r="C2046" t="n">
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.33512322712102</v>
+        <v>-4.261595800490737</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.111572379363995</v>
+        <v>2.140983350016108</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.022686391720298</v>
+        <v>0.9936832014359143</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.459589929558329</v>
+        <v>4.442188015387699</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760316</v>
+        <v>3.646857607760315</v>
       </c>
       <c r="C2047" t="n">
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.358565266301107</v>
+        <v>-4.285037839670824</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.122398233865554</v>
+        <v>2.151809204517668</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.022686391720298</v>
+        <v>0.9936832014359143</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.479792599731923</v>
+        <v>4.462390685561293</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781707</v>
+        <v>3.666767386781706</v>
       </c>
       <c r="C2048" t="n">
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.376637774592719</v>
+        <v>-4.303110347962435</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.11516923054891</v>
+        <v>2.144580201201023</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.022686391720298</v>
+        <v>0.9936832014359143</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.479792599731923</v>
+        <v>4.462390685561293</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082836</v>
+        <v>3.670068888082835</v>
       </c>
       <c r="C2049" t="n">
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.607811568469351</v>
+        <v>-4.534284141839067</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.982951626591723</v>
+        <v>2.012362597243837</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.022686391720298</v>
+        <v>0.9936832014359143</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.440044513325391</v>
+        <v>4.422642599154759</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.576525547928895</v>
+        <v>-4.502998121298612</v>
       </c>
       <c r="E2050" t="n">
-        <v>2.002488653804845</v>
+        <v>2.031899624456959</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.053972412260753</v>
+        <v>1.02496922197637</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.465838744646604</v>
+        <v>4.448436830475973</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.423500155815611</v>
+        <v>-4.349972729185327</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.162869810223063</v>
+        <v>2.192280780875177</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.206997804374037</v>
+        <v>1.177994614089654</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.656824979487478</v>
+        <v>4.639423065316848</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>4.120092521771348</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.451807469688881</v>
+        <v>-4.378280043058598</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.339013109582048</v>
+        <v>2.368424080234161</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.206997804374037</v>
+        <v>1.177994614089654</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.844291204395771</v>
+        <v>4.82688929022514</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>4.08949547312543</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.618400694802403</v>
+        <v>-4.54487326817212</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.241778770890721</v>
+        <v>2.271189741542835</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.040404579260515</v>
+        <v>1.011401388976131</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.713738220681739</v>
+        <v>4.696336306511109</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>4.093171875787148</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.445336315420104</v>
+        <v>-4.37180888878982</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.314680925305359</v>
+        <v>2.344091895957472</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.040404579260515</v>
+        <v>1.011401388976131</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.717414623343457</v>
+        <v>4.700012709172826</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>4.090789930910643</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.416090334964407</v>
+        <v>-4.342562908334124</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.323997372611132</v>
+        <v>2.353408343263246</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.040404579260515</v>
+        <v>1.011401388976131</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.715032678466952</v>
+        <v>4.697630764296322</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>4.088083170068278</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.523015882842258</v>
+        <v>-4.449488456211975</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.278520392617628</v>
+        <v>2.30793136326974</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.9334790313826636</v>
+        <v>0.9044758410982799</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.648170588897877</v>
+        <v>4.630768674727246</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>4.089511972211512</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.668034441349507</v>
+        <v>-4.594507014719223</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.221941771357962</v>
+        <v>2.251352742010075</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.7884604728754151</v>
+        <v>0.7594572825910314</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.562588255936761</v>
+        <v>4.545186341766131</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>4.189443211469265</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.786376207134224</v>
+        <v>-4.712848780503941</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.274536304301828</v>
+        <v>2.303947274953941</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.7991465114383052</v>
+        <v>0.7701433211539215</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.668931118332249</v>
+        <v>4.651529204161618</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>4.187228908595204</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.837786629454932</v>
+        <v>-4.764259202824649</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.251757832499484</v>
+        <v>2.281168803151597</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.7991465114383052</v>
+        <v>0.7701433211539215</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.666716815458187</v>
+        <v>4.649314901287557</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>4.187132036669493</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.917206080662684</v>
+        <v>-4.8436786540324</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.219893180090672</v>
+        <v>2.249304150742786</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.7991465114383052</v>
+        <v>0.7701433211539215</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.666619943532477</v>
+        <v>4.649218029361847</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>4.187125930227537</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.012669078579902</v>
+        <v>-4.939141651949618</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.181701874481829</v>
+        <v>2.211112845133942</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.7991465114383052</v>
+        <v>0.7701433211539215</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.66661383709052</v>
+        <v>4.64921192291989</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>4.185222326790147</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.052689076623685</v>
+        <v>-4.979161649993402</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.163790271826926</v>
+        <v>2.19320124247904</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.7591265133945213</v>
+        <v>0.7301233231101376</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.640698234826861</v>
+        <v>4.62329632065623</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,19 +48994,19 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.831171972203367</v>
+        <v>3.831171972203366</v>
       </c>
       <c r="C2063" t="n">
         <v>4.312399423030092</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.052689076623685</v>
+        <v>-4.979161649993402</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.163790271826926</v>
+        <v>2.19320124247904</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.7591265133945213</v>
+        <v>0.7301233231101376</v>
       </c>
       <c r="G2063" t="n">
         <v>4.30546322001646</v>

--- a/tame_output/ON/bt/strategyON_20240821.xlsx
+++ b/tame_output/ON/bt/strategyON_20240821.xlsx
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>98.3%</t>
+          <t>94.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>40.1%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>80.8%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>119.6%</t>
+          <t>107.5%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.3%</t>
+          <t>-78.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-42.4%</t>
+          <t>-46.2%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.2%</t>
+          <t>-48.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.4%</t>
+          <t>-74.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-3.0%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-659.5%</t>
+          <t>-665.5%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>25.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-156.9%</t>
+          <t>-158.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>81.5%</t>
+          <t>94.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>60.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.4%</t>
+          <t>-1.0%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-21.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>74.7%</t>
+          <t>85.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-15.5%</t>
+          <t>16.9%</t>
         </is>
       </c>
     </row>
@@ -48626,7 +48626,7 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760315</v>
+        <v>3.646857607760314</v>
       </c>
       <c r="C2047" t="n">
         <v>3.866180764699744</v>
@@ -48649,7 +48649,7 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781706</v>
+        <v>3.666767386781705</v>
       </c>
       <c r="C2048" t="n">
         <v>3.866180764699744</v>
@@ -48672,7 +48672,7 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082835</v>
+        <v>3.670068888082834</v>
       </c>
       <c r="C2049" t="n">
         <v>3.826432678293211</v>
@@ -48695,7 +48695,7 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943587</v>
+        <v>3.745593333943585</v>
       </c>
       <c r="C2050" t="n">
         <v>3.833455297290151</v>
@@ -48718,7 +48718,7 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677825</v>
+        <v>3.730590658677824</v>
       </c>
       <c r="C2051" t="n">
         <v>3.932626296863055</v>
@@ -48741,7 +48741,7 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073885</v>
+        <v>3.741298518073883</v>
       </c>
       <c r="C2052" t="n">
         <v>4.120092521771348</v>
@@ -48764,7 +48764,7 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.69913580090317</v>
+        <v>3.699135800903168</v>
       </c>
       <c r="C2053" t="n">
         <v>4.08949547312543</v>
@@ -48787,7 +48787,7 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568384</v>
+        <v>3.708202704568382</v>
       </c>
       <c r="C2054" t="n">
         <v>4.093171875787148</v>
@@ -48810,7 +48810,7 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740601586682206</v>
+        <v>3.740601586682204</v>
       </c>
       <c r="C2055" t="n">
         <v>4.090789930910643</v>
@@ -48833,7 +48833,7 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539109</v>
+        <v>3.699424827539107</v>
       </c>
       <c r="C2056" t="n">
         <v>4.088083170068278</v>
@@ -48856,7 +48856,7 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983739</v>
+        <v>3.689962785983737</v>
       </c>
       <c r="C2057" t="n">
         <v>4.089511972211512</v>
@@ -48879,7 +48879,7 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.71187261496975</v>
+        <v>3.711872614969749</v>
       </c>
       <c r="C2058" t="n">
         <v>4.189443211469265</v>
@@ -48902,7 +48902,7 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.71489923707354</v>
+        <v>3.714899237073539</v>
       </c>
       <c r="C2059" t="n">
         <v>4.187228908595204</v>
@@ -48925,7 +48925,7 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704778134720067</v>
+        <v>3.704778134720065</v>
       </c>
       <c r="C2060" t="n">
         <v>4.187132036669493</v>
@@ -48948,7 +48948,7 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736825137581135</v>
+        <v>3.736825137581133</v>
       </c>
       <c r="C2061" t="n">
         <v>4.187125930227537</v>
@@ -48971,7 +48971,7 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715393145500737</v>
+        <v>3.715393145500735</v>
       </c>
       <c r="C2062" t="n">
         <v>4.185222326790147</v>
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.831171972203366</v>
+        <v>3.831171972203364</v>
       </c>
       <c r="C2063" t="n">
-        <v>4.312399423030092</v>
+        <v>4.190956144537874</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.979161649993402</v>
+        <v>-5.03893955471165</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.19320124247904</v>
+        <v>2.175023898339467</v>
       </c>
       <c r="F2063" t="n">
         <v>0.7301233231101376</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.30546322001646</v>
+        <v>4.629030138403957</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240821.xlsx
+++ b/tame_output/ON/bt/strategyON_20240821.xlsx
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-46.2%</t>
+          <t>-46.3%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -48534,7 +48534,7 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912983</v>
+        <v>3.785761685912982</v>
       </c>
       <c r="C2043" t="n">
         <v>3.837559870562694</v>
@@ -48557,7 +48557,7 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539893</v>
+        <v>3.743767956539892</v>
       </c>
       <c r="C2044" t="n">
         <v>3.831246438464132</v>
@@ -48580,7 +48580,7 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811007</v>
+        <v>3.725010844811006</v>
       </c>
       <c r="C2045" t="n">
         <v>3.833127068648268</v>
@@ -48603,7 +48603,7 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382918</v>
+        <v>3.612322444382917</v>
       </c>
       <c r="C2046" t="n">
         <v>3.84597809452615</v>
@@ -48626,7 +48626,7 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760314</v>
+        <v>3.646857607760313</v>
       </c>
       <c r="C2047" t="n">
         <v>3.866180764699744</v>
@@ -48994,16 +48994,16 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.831171972203364</v>
+        <v>3.831171972203365</v>
       </c>
       <c r="C2063" t="n">
         <v>4.190956144537874</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.03893955471165</v>
+        <v>-5.039454197745799</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.175023898339467</v>
+        <v>2.174818041125807</v>
       </c>
       <c r="F2063" t="n">
         <v>0.7301233231101376</v>
